--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_586_Pakistan.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_586_Pakistan.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R19338f978c3b4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbd6f75c8e6a74f06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8d2f3a7809274c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8b2259f4ddd64514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R71c83baf2b944d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R7ee4467199524841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R4ae269dd75c54aef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc7e48a0cfc2b4372"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf0ea9923d88b4a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R40cbe4b3294b462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R543671e8c4994d66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5377f7c2360b4aaa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ586CommercialTable" displayName="EEZ586CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ586CommercialTable" displayName="EEZ586CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ586FunctionalTable" displayName="EEZ586FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ586FunctionalTable" displayName="EEZ586FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ586ValidationTable" displayName="EEZ586ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ586ValidationTable" displayName="EEZ586ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -9136,7 +9090,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bba54c14a12441f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a94c27850aa4362"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9146,20 +9100,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9167,552 +9111,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>13319.850907572501</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3012408515719285</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>200.09712631024962</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>13319.850907572501</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>207.3938812235864</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$127,A2,'Species'!$U$2:$U$127))</x:f>
-        <x:v>2762455.577040971</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3012408515719285</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>200.09712631024962</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2665263.8894862277</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>97191.68755474314</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0364660654947297</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.036466065494729825</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>30471.724710023394</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3040548212524445</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>201.3978459524162</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>30471.724710023394</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>222.8137843297797</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$127,A3,'Species'!$U$2:$U$127))</x:f>
-        <x:v>6789520.297695572</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3040548212524445</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>201.3978459524162</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6136939.719053726</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>652580.5786418458</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.106336481783541</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10633648178354102</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3114.1654108236</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.483782070907814</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>304.6365938742999</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3114.1654108236</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>763.9875082246149</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$127,A4,'Species'!$U$2:$U$127))</x:f>
-        <x:v>2379183.472414406</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.483782070907814</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>304.6365938742999</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>948688.7435144612</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1430494.7288999448</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.507865186215461</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.507865186215461</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>267564.6168480039</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.634707140530592</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>43.122818699739575</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>267564.6168480039</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>77.20956253733803</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$127,A5,'Species'!$U$2:$U$127))</x:f>
-        <x:v>20658547.017304845</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.634707140530592</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>43.122818699739575</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>11538140.462801756</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>9120406.554503089</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.7904572304269228</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.7904572304269227</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>8167.8719948364005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.2167370595341684</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>16.471648254923814</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>8167.8719948364005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>16.579794611867673</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$127,A6,'Species'!$U$2:$U$127))</x:f>
-        <x:v>135421.64009041342</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.2167370595341684</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>16.471648254923814</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>134538.3144901881</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>883.3256002253329</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0065656062629635</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006565606262963508</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>119703.19656090299</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.529319200910791</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>338.31340088800835</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>119703.19656090299</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>503.1323487573418</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$127,A7,'Species'!$U$2:$U$127))</x:f>
-        <x:v>60226550.43944888</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.529319200910791</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>338.31340088800835</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>40497195.52568483</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>19729354.913764045</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.487178301056698</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.4871783010566979</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>382322.1368853781</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7823547637035126</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>605.8355637644206</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>382322.1368853781</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1151.7834980597686</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$127,A8,'Species'!$U$2:$U$127))</x:f>
-        <x:v>440352328.2075265</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7823547637035126</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>605.8355637644206</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>231624347.33957103</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>208727980.86795548</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.9011487059344045</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.9011487059344045</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>100374.50618217808</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.331260723321762</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2144.1774452254617</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>100374.50618217808</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2410.432407704337</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$127,A9,'Species'!$U$2:$U$127))</x:f>
-        <x:v>241945962.6088414</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.331260723321762</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2144.1774452254617</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>215220752.23146993</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>26725210.37737146</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1241758060051221</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12417580600512211</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5302.2236583629</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.449621409199347</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2815.927111648875</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5302.2236583629</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2831.1370635030316</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$127,A10,'Species'!$U$2:$U$127))</x:f>
-        <x:v>15011321.918173842</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.449621409199347</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2815.927111648875</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>14930675.351610173</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>80646.56656366959</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0054014011198076</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.005401401119807511</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc38f51449d3149f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55546246893a404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9722,20 +9307,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9743,1200 +9318,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>17012.2306581439</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.734463821311103</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>542.5800500812409</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>17012.2306581439</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>555.3166342644284</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$127,A2,'Species'!$U$2:$U$127))</x:f>
-        <x:v>9447174.670410594</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.734463821311103</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>542.5800500812409</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>9230496.962489339</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>216677.70792125538</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.023474110744176</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.02347411074417605</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>7499.952777328501</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.1421800433942977</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>138.73308488124874</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>7499.952777328501</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>203.3928094480578</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$127,A3,'Species'!$U$2:$U$127))</x:f>
-        <x:v>1525436.4661086076</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.1421800433942977</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>138.73308488124874</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1040491.5852624722</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>484944.88084613543</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4660728522122592</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.46607285221225914</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>32562.427824980296</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.156056056536478</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1432.3727707791265</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>32562.427824980296</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2085.244566786339</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$127,A4,'Species'!$U$2:$U$127))</x:f>
-        <x:v>67900625.70341247</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.156056056536478</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1432.3727707791265</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>46641534.96696235</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>21259090.73645012</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4557974078577944</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.45579740785779443</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>32620.507851792903</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7829623453687744</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>606.6837260135226</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>32620.507851792903</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>875.8599177201603</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$127,A5,'Species'!$U$2:$U$127))</x:f>
-        <x:v>28570995.323061176</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7829623453687744</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>606.6837260135226</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>19790331.247979086</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>8780664.07508209</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.4436845429749308</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.44368454297493065</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>72992.0089761436</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.359969926018347</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.7090204819624</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>72992.0089761436</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2451.86879346004</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$127,A6,'Species'!$U$2:$U$127))</x:f>
-        <x:v>178966828.98056158</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.359969926018347</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.7090204819624</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>167203453.3847525</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>11763375.595809072</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0703536641001088</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07035366410010876</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5887.808809347401</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4745570700303485</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>298.2339427229127</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5887.808809347401</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>315.0282569885281</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$127,A7,'Species'!$U$2:$U$127))</x:f>
-        <x:v>1854826.1466904127</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4745570700303485</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>298.2339427229127</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1755944.4352103733</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>98881.7114800394</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0563125515234157</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0563125515234158</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>14370.2191106799</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.0655941398095505</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1163.038629659453</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>14370.2191106799</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1669.9137779129376</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$127,A8,'Species'!$U$2:$U$127))</x:f>
-        <x:v>23997026.884552166</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.0655941398095505</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1163.038629659453</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>16713119.942391234</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>7283906.942160932</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4358197013644352</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.4358197013644351</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>94486.69737283068</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.384645035157173</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2424.627547774882</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>94486.69737283068</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2541.0046402065095</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$127,A9,'Species'!$U$2:$U$127))</x:f>
-        <x:v>240091136.46215096</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.384645035157173</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2424.627547774882</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>229095049.34843382</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>10996087.113717139</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.047997925511664</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.047997925511664104</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9474.7563517499</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.311562061260801</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>204.90948474235674</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9474.7563517499</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>268.9096912322565</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$127,A10,'Species'!$U$2:$U$127))</x:f>
-        <x:v>2547853.8050499265</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.311562061260801</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>204.90948474235674</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1941467.4420964438</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>606386.3629534827</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.31233403651554</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.31233403651554</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1115.9427866028</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1115.9427866028</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$127,A11,'Species'!$U$2:$U$127))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1341658.323400396</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>1341658.323400396</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>20969.5034210141</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3345563695107066</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>216.05104413149294</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>20969.5034210141</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>301.014195845642</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$127,A12,'Species'!$U$2:$U$127))</x:f>
-        <x:v>6312118.209558997</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3345563695107066</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>216.05104413149294</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4530483.109029009</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1781635.1005299883</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3932549923824427</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3932549923824427</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>112009.0595162127</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.528886706783756</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>337.9766576567353</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>112009.0595162127</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>438.58730214275266</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$127,A13,'Species'!$U$2:$U$127))</x:f>
-        <x:v>49125751.228762746</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.528886706783756</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>337.9766576567353</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>37856447.56256391</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>11269303.666198835</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2976851868515789</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.29768518685157885</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>110368.217533344</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4543925938478584</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>284.7033608079837</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>110368.217533344</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>591.8183112702311</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$127,A14,'Species'!$U$2:$U$127))</x:f>
-        <x:v>65317932.11848915</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4543925938478584</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>284.7033608079837</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>31422202.458129667</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>33895729.66035949</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.0787190906024433</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.078719090602443</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>59763.42165909611</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6696864234901603</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>467.39754129189595</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>59763.42165909611</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1034.794042184764</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$127,A15,'Species'!$U$2:$U$127))</x:f>
-        <x:v>61842832.67340854</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6696864234901603</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>467.39754129189595</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>27933276.34265236</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>33909556.33075617</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.2139484074404265</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.2139484074404263</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>8167.8719948364005</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.2167370595341684</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>16.471648254923814</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>8167.8719948364005</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>16.579794611867673</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$127,A16,'Species'!$U$2:$U$127))</x:f>
-        <x:v>135421.64009041342</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.2167370595341684</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>16.471648254923814</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>134538.3144901881</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>883.3256002253329</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0065656062629635</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.006565606262963508</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>20996.968358273498</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3006672241127237</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>199.83300728203352</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>20996.968358273498</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>202.01328212100148</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$127,A17,'Species'!$U$2:$U$127))</x:f>
-        <x:v>4241666.4926456455</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3006672241127237</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>199.83300728203352</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4195887.330839495</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>45779.16180615034</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0109104840517706</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.010910484051770532</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>3529.3616608437997</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>3529.3616608437997</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>173.78008287493765</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$127,A18,'Species'!$U$2:$U$127))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>613332.761917063</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>613332.761917063</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>15081.0556371901</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.588430920731447</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>387.64208490979934</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>15081.0556371901</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>403.20699367198</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$127,A19,'Species'!$U$2:$U$127))</x:f>
-        <x:v>6080787.104871287</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.588430920731447</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>387.64208490979934</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>5846051.849841053</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>234735.25503023434</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0401527836323614</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.04015278363236147</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>276344.27633926825</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.7080502453605275</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>51.05640658689617</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>276344.27633926825</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>132.1916127248318</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$127,A20,'Species'!$U$2:$U$127))</x:f>
-        <x:v>36530395.55656445</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.7080502453605275</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>51.05640658689617</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>14109145.730739271</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>22421249.825825177</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>2.589128800121223</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>1.5891288001212232</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>11973.8391075795</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.868863562368091</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>73.93729577085217</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>11973.8391075795</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>120.1208018157999</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$127,A21,'Species'!$U$2:$U$127))</x:f>
-        <x:v>1438307.1544158314</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.868863562368091</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>73.93729577085217</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>885313.2836097021</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>552993.8708061293</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.6246307166559146</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.6246307166559147</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>3114.1654108236</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.483782070907814</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>304.6365938742999</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>3114.1654108236</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>763.9875082246149</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$127,A22,'Species'!$U$2:$U$127))</x:f>
-        <x:v>2379183.472414406</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.483782070907814</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>304.6365938742999</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>948688.7435144612</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1430494.7288999448</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>2.507865186215461</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>1.507865186215461</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7e50ae69ff47bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R593be6758be44aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11111,7 +9907,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -11210,7 +10006,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>790261291.1785368</x:v>
+        <x:v>523696541.5776824</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11224,7 +10020,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>790261291.1785369</x:v>
+        <x:v>623228915.1263041</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11238,7 +10034,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-266564749.6008544</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11252,7 +10048,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-167032376.05223262</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -11263,9 +10059,9 @@
         <x:v>EEZ_586</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -11277,47 +10073,19 @@
         <x:v>EEZ_586</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_586</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_586</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8655cccfa994a4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R998d18a5d8dc4fe8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11364,7 +10132,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
